--- a/inbox/new_batch.xlsx
+++ b/inbox/new_batch.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="87">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -690,6 +690,9 @@
       <c r="D5" t="s">
         <v>69</v>
       </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
@@ -704,6 +707,9 @@
       <c r="D6" t="s">
         <v>69</v>
       </c>
+      <c r="E6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
@@ -718,6 +724,9 @@
       <c r="D7" t="s">
         <v>71</v>
       </c>
+      <c r="E7" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
@@ -732,6 +741,9 @@
       <c r="D8" t="s">
         <v>72</v>
       </c>
+      <c r="E8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
@@ -746,6 +758,9 @@
       <c r="D9" t="s">
         <v>73</v>
       </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
@@ -760,6 +775,9 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
+      <c r="E10" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
@@ -774,6 +792,9 @@
       <c r="D11" t="s">
         <v>74</v>
       </c>
+      <c r="E11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
@@ -788,6 +809,9 @@
       <c r="D12" t="s">
         <v>75</v>
       </c>
+      <c r="E12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
@@ -802,6 +826,9 @@
       <c r="D13" t="s">
         <v>76</v>
       </c>
+      <c r="E13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
@@ -816,6 +843,9 @@
       <c r="D14" t="s">
         <v>77</v>
       </c>
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
@@ -830,6 +860,9 @@
       <c r="D15" t="s">
         <v>77</v>
       </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
@@ -844,8 +877,11 @@
       <c r="D16" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -858,8 +894,11 @@
       <c r="D17" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -872,8 +911,11 @@
       <c r="D18" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -886,8 +928,11 @@
       <c r="D19" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -900,8 +945,11 @@
       <c r="D20" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -914,8 +962,11 @@
       <c r="D21" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -928,8 +979,11 @@
       <c r="D22" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -942,8 +996,11 @@
       <c r="D23" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -956,8 +1013,11 @@
       <c r="D24" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -970,8 +1030,11 @@
       <c r="D25" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -984,8 +1047,11 @@
       <c r="D26" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -999,7 +1065,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1013,7 +1079,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>

--- a/inbox/new_batch.xlsx
+++ b/inbox/new_batch.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="87">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1064,6 +1064,9 @@
       <c r="D27" t="s">
         <v>85</v>
       </c>
+      <c r="E27" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
@@ -1078,6 +1081,9 @@
       <c r="D28" t="s">
         <v>85</v>
       </c>
+      <c r="E28" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
@@ -1091,6 +1097,9 @@
       </c>
       <c r="D29" t="s">
         <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
